--- a/github_clone_history_all_repos.xlsx
+++ b/github_clone_history_all_repos.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,6 +857,125 @@
       </c>
       <c r="E25" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -870,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,6 +1425,125 @@
       </c>
       <c r="E25" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1319,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,6 +1993,125 @@
       </c>
       <c r="E25" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1768,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2204,6 +2561,125 @@
       </c>
       <c r="E25" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2217,7 +2693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2638,6 +3114,125 @@
         <v>12</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>13</v>
+      </c>
+      <c r="E27" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>13</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>13</v>
+      </c>
+      <c r="E29" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>13</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>14</v>
+      </c>
+      <c r="E31" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
